--- a/buoi9/BUOI9_NguyenThuyKieu.xlsx
+++ b/buoi9/BUOI9_NguyenThuyKieu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hoc_tap\Hoctap2025\nam4\quanliduanphanmem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C777716-0A2B-4E8E-AC9A-9CDB7DC50D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916E3EAE-0E8B-4962-B4CF-05CBEA9669EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WSM_Project" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,9 @@
     <sheet name="NPV" sheetId="3" r:id="rId3"/>
     <sheet name="ROI" sheetId="4" r:id="rId4"/>
     <sheet name="Paypack" sheetId="5" r:id="rId5"/>
+    <sheet name="KICK-OFF MEETING" sheetId="6" r:id="rId6"/>
+    <sheet name="TEAM CONTRACT" sheetId="7" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="85">
   <si>
     <t>Mô hình trọng số - WSM (Dự án)</t>
   </si>
@@ -194,6 +193,398 @@
   </si>
   <si>
     <t>Năm 0</t>
+  </si>
+  <si>
+    <t>BIÊN BẢN HỌP KHỞI ĐỘNG DỰ ÁN (KICK-OFF MEETING) 
+27/10/2025</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tên dự án:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Ứng dụng dự báo Thời tiết Sài Gòn bằng LSTM -Flutter
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mục tiêu buổi họp:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Khởi động dự án một cách hiệu quả bằng cách giới thiệu các bên liên quan chính, rà soát mục tiêu dự án, thống nhất phạm vi, thời gian, chi phí, và kế hoạch hành động trong các giai đoạn sắp tới.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nội dung chương trình:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Giới thiệu thành phần tham dự.
+- Trình bày bối cảnh và lý do thực hiện dự án.
+- Rà soát các tài liệu liên quan (Project Charter, Business Case, Kế hoạch tổng thể).
+- Thảo luận về cơ cấu tổ chức và vai trò trong dự án.
+- Thống nhất phạm vi, tiến độ, mục tiêu chi phí của dự án.
+- Trao đổi các vấn đề quan trọng khác (rủi ro, truyền thông, báo cáo tiến độ).
+- Ghi nhận danh sách các công việc hành động (Action Items) cần thực hiện sau cuộc họp.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Danh sách công việc sau cuộc họp
+</t>
+    </r>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Công việc cần thực hiện</t>
+  </si>
+  <si>
+    <t>Người phụ trách</t>
+  </si>
+  <si>
+    <t>Thời hạn hoàn thành</t>
+  </si>
+  <si>
+    <t>Chuẩn bị tài liệu chi tiết mô hình LSTM và dữ liệu thời tiết</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn A</t>
+  </si>
+  <si>
+    <t>Thiết lập cơ sở dữ liệu PostgreSQL và API FastAPI</t>
+  </si>
+  <si>
+    <t>Trần Thị B</t>
+  </si>
+  <si>
+    <t>15/11/2025</t>
+  </si>
+  <si>
+    <t>Thiết kế giao diện Flutter – màn hình hiển thị thời tiết</t>
+  </si>
+  <si>
+    <t>Lê Văn C</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
+  </si>
+  <si>
+    <t>Báo cáo tiến độ giai đoạn 1 cho giảng viên hướng dẫn</t>
+  </si>
+  <si>
+    <t>Nhóm dự án</t>
+  </si>
+  <si>
+    <t>30/11/2025</t>
+  </si>
+  <si>
+    <t>HỢP ĐỒNG LÀM VIỆC NHÓM (TEAM CONTRACT)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tên dự án:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Ứng dụng Dự Báo Thời Tiết TP.HCM bằng LSTM – Flutter
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Thành viên nhóm &amp; Xác nhận cam kết: 
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Họ và tên</t>
+  </si>
+  <si>
+    <t>Xác nhận tham gia (Ký tên)</t>
+  </si>
+  <si>
+    <t>Trần Văn B</t>
+  </si>
+  <si>
+    <t>- Làm việc chủ động, dự đoán trước các vấn đề tiềm ẩn và tìm cách ngăn ngừa chúng.
+- Luôn cập nhật thông tin kịp thời cho các thành viên khác về tiến độ và vấn đề dự án.
+- Hành động vì lợi ích chung của toàn bộ nhóm và dự án.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I. Quy tắc ứng xử:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Là nhóm dự án, chúng tôi cam kết:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>II. Tham gia &amp; Hợp tác:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Chúng tôi sẽ:</t>
+    </r>
+  </si>
+  <si>
+    <t>- Trung thực và cởi mở trong mọi hoạt động của dự án.
+- Khuyến khích sự đa dạng và tôn trọng ý kiến của mọi thành viên.
+- Tạo cơ hội để mọi người cùng đóng góp và tham gia bình đẳng.
+- Luôn cởi mở với các ý tưởng mới, sáng tạo.
+- Mỗi lần chỉ thảo luận một chủ đề để đảm bảo hiệu quả.
+- Thông báo sớm cho Trưởng nhóm nếu không thể tham dự cuộc họp hoặc có nguy cơ trễ hạn giao nhiệm vụ.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">III. Giao tiếp (Communication):
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nhóm thống nhất sẽ:</t>
+    </r>
+  </si>
+  <si>
+    <t>- Cùng nhau lựa chọn hình thức giao tiếp phù hợp (trực tiếp, email, nhóm Zalo, Google Meet...).
+- Sử dụng kênh nhóm (Zalo / Google Meet) để trao đổi, cập nhật tiến độ hàng tuần.
+- Trưởng nhóm sẽ phụ trách điều phối các cuộc họp và thông báo nội dung, thời gian cụ thể.
+- Mỗi thành viên phải báo cáo tiến độ công việc trước 17h thứ Sáu hàng tuần.
+- Thể hiện ý tưởng một cách rõ ràng, ngắn gọn, tôn trọng người khác.
+- Duy trì các cuộc thảo luận đúng trọng tâm, tập trung vào kết quả.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IV. Giải quyết vấn đề:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Chúng tôi sẽ:</t>
+    </r>
+  </si>
+  <si>
+    <t>- Khuyến khích tất cả các thành viên cùng tham gia tìm giải pháp cho vấn đề.
+- Chỉ sử dụng phản hồi mang tính xây dựng, tránh đổ lỗi cho cá nhân.
+- Luôn tìm cách cải thiện và phát triển dự án dựa trên ý kiến đóng góp của nhóm.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">V. Hướng dẫn họp nhóm:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nhóm sẽ:</t>
+    </r>
+  </si>
+  <si>
+    <t>- Tổ chức họp trực tiếp hoặc online vào thứ Ba đầu tiên và thứ Ba giữa tháng.
+- Họp nhiều hơn trong tháng đầu tiên để thống nhất quy trình làm việc.
+- Sử dụng Google Meet / Zoom cho thành viên không thể tham dự trực tiếp.
+- Ghi biên bản họp và gửi lại qua email/nhóm Zalo trong vòng 24 giờ sau mỗi buổi họp.
+- Trong biên bản họp phải nêu rõ: các quyết định đã thống nhất, nhiệm vụ giao cụ thể, và thời hạn hoàn thành.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ngày và thời gian dự kiến của buổi họp tiếp theo: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>30/11/2025 tại Zoom.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -216,6 +607,7 @@
       <b/>
       <sz val="13"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -229,6 +621,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -253,12 +646,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="6">
@@ -336,12 +735,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -354,6 +750,30 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -363,14 +783,60 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,13 +935,6 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>WSM_Project!$A$10</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
               <c:f>WSM_Project!$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
@@ -487,13 +946,6 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>WSM_Project!$D$10</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
               <c:f>WSM_Project!$D$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
@@ -1939,169 +2391,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="NPV"/>
-      <sheetName val="ROI"/>
-      <sheetName val="Payback"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="B2" t="str">
-            <v>YEAR 1</v>
-          </cell>
-          <cell r="C2" t="str">
-            <v>YEAR 2</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>YEAR 3</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>YEAR 4</v>
-          </cell>
-          <cell r="F2" t="str">
-            <v>YEAR 5</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>0</v>
-          </cell>
-          <cell r="C6">
-            <v>12396000</v>
-          </cell>
-          <cell r="D6">
-            <v>15026000</v>
-          </cell>
-          <cell r="E6">
-            <v>17075000</v>
-          </cell>
-          <cell r="F6">
-            <v>18627000</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>27273000</v>
-          </cell>
-          <cell r="C7">
-            <v>8264000</v>
-          </cell>
-          <cell r="D7">
-            <v>6010400</v>
-          </cell>
-          <cell r="E7">
-            <v>5464000</v>
-          </cell>
-          <cell r="F7">
-            <v>4967200</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="B2" t="str">
-            <v>YEAR 1</v>
-          </cell>
-          <cell r="C2" t="str">
-            <v>YEAR 2</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>YEAR 3</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>YEAR 4</v>
-          </cell>
-          <cell r="F2" t="str">
-            <v>YEAR 5</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>27273000</v>
-          </cell>
-          <cell r="C6">
-            <v>35537000</v>
-          </cell>
-          <cell r="D6">
-            <v>41547400</v>
-          </cell>
-          <cell r="E6">
-            <v>47011400</v>
-          </cell>
-          <cell r="F6">
-            <v>51978600</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>0</v>
-          </cell>
-          <cell r="C7">
-            <v>12396000</v>
-          </cell>
-          <cell r="D7">
-            <v>27422000</v>
-          </cell>
-          <cell r="E7">
-            <v>44497000</v>
-          </cell>
-          <cell r="F7">
-            <v>63124000</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2">
-        <row r="1">
-          <cell r="D1" t="str">
-            <v>Tổng chi phí lũy kế</v>
-          </cell>
-          <cell r="E1" t="str">
-            <v>Tổng lợi ích lũy kế</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2">
-            <v>0</v>
-          </cell>
-          <cell r="D2">
-            <v>140000</v>
-          </cell>
-          <cell r="E2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>1</v>
-          </cell>
-          <cell r="D3">
-            <v>140000</v>
-          </cell>
-          <cell r="E3">
-            <v>172000</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>2</v>
-          </cell>
-          <cell r="D4">
-            <v>140000</v>
-          </cell>
-          <cell r="E4">
-            <v>415500</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2397,146 +2686,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>25</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>90</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <f>B3%*C3</f>
         <v>22.5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>15</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>70</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <f t="shared" ref="D4:D9" si="0">B4%*C4</f>
         <v>10.5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>15</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>90</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>10</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>80</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>5</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>90</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>20</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>80</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>10</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>70</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>100</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5">
         <f>SUM(D3:D9)</f>
         <v>82</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -2561,70 +2851,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>25</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>90</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <f xml:space="preserve"> B3% * C3</f>
         <v>22.5</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>80</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <f xml:space="preserve"> B3% *E3</f>
         <v>20</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>80</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <f>B3% * G3</f>
         <v>20</v>
       </c>
@@ -2633,30 +2923,30 @@
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>20</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>80</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <f t="shared" ref="D4:D9" si="0" xml:space="preserve"> B4% * C4</f>
         <v>16</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>80</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <f t="shared" ref="F4:F9" si="1" xml:space="preserve"> B4% *E4</f>
         <v>16</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>90</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <f t="shared" ref="H4:H9" si="2">B4% * G4</f>
         <v>18</v>
       </c>
@@ -2668,30 +2958,30 @@
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>15</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>80</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>100</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>100</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
@@ -2703,30 +2993,30 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>10</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>90</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>90</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>90</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
@@ -2738,30 +3028,30 @@
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>10</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>100</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>100</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>100</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
@@ -2773,30 +3063,30 @@
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>10</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>80</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>80</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>70</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
@@ -2808,30 +3098,30 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>10</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>90</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>80</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>90</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
@@ -2843,25 +3133,25 @@
       <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <f xml:space="preserve"> SUM(B3:B9)</f>
         <v>100</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5">
         <f xml:space="preserve"> SUM(D3:D9)</f>
         <v>86.5</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6">
-        <f t="shared" ref="E10:N10" si="3" xml:space="preserve"> SUM(F3:F9)</f>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5">
+        <f t="shared" ref="F10:H10" si="3" xml:space="preserve"> SUM(F3:F9)</f>
         <v>86</v>
       </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6">
+      <c r="G10" s="5"/>
+      <c r="H10" s="5">
         <f t="shared" si="3"/>
         <v>88</v>
       </c>
@@ -2894,124 +3184,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="7">
+      <c r="B1" s="6">
         <v>0.1</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>0</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>100000</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>200000</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>300000</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>400000</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <f xml:space="preserve"> SUM(B4:F4)</f>
         <v>1000000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>50000</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>50000</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>50000</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>50000</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>50000</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <f xml:space="preserve"> SUM(B5:F5)</f>
         <v>250000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <f>- B5</f>
         <v>-50000</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <f xml:space="preserve"> C5</f>
         <v>50000</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <f t="shared" ref="D6:F6" si="0">C6 + D5</f>
         <v>100000</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <f t="shared" si="0"/>
         <v>150000</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <f t="shared" si="0"/>
         <v>200000</v>
       </c>
-      <c r="G6" s="6">
-        <f t="shared" ref="G5:G6" si="1" xml:space="preserve"> SUM(B6:F6)</f>
+      <c r="G6" s="5">
+        <f t="shared" ref="G6" si="1" xml:space="preserve"> SUM(B6:F6)</f>
         <v>450000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="24">
         <f>NPV(B1,B6:F6)</f>
         <v>297635.53160179057</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="13"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="26"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
@@ -3035,263 +3325,264 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="14">
+      <c r="B1" s="10">
         <v>0.1</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="14"/>
+      <c r="A2" s="10"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>50000</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>50000</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>50000</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>50000</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>50000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="12">
         <v>0.91</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="12">
         <v>0.83</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="12">
         <v>0.75</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="12">
         <v>0.68</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <f>B4*B5</f>
         <v>50000</v>
       </c>
-      <c r="C6" s="6">
-        <f t="shared" ref="C6:F8" si="0">C4*C5</f>
+      <c r="C6" s="5">
+        <f t="shared" ref="C6:F6" si="0">C4*C5</f>
         <v>45500</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <f t="shared" si="0"/>
         <v>41500</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <f t="shared" si="0"/>
         <v>37500</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <f t="shared" si="0"/>
         <v>34000</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="13">
         <f>SUM(B6:F6)</f>
         <v>208500</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="14"/>
-      <c r="G7" s="17"/>
+      <c r="A7" s="10"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>0</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>200000</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>200000</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>200000</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>200000</v>
       </c>
-      <c r="G8" s="17"/>
+      <c r="G8" s="13"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="11">
         <v>1</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="12">
         <v>0.91</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="12">
         <v>0.83</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="12">
         <v>0.75</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="12">
         <v>0.68</v>
       </c>
-      <c r="G9" s="17"/>
+      <c r="G9" s="13"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <f>B8*B9</f>
         <v>0</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <f t="shared" ref="C10:F10" si="1">C8*C9</f>
         <v>182000</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <f t="shared" si="1"/>
         <v>166000</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <f t="shared" si="1"/>
         <v>150000</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <f t="shared" si="1"/>
         <v>136000</v>
       </c>
-      <c r="G10" s="17">
-        <f t="shared" ref="G7:G13" si="2">SUM(B10:F10)</f>
+      <c r="G10" s="13">
+        <f t="shared" ref="G10" si="2">SUM(B10:F10)</f>
         <v>634000</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="14"/>
-      <c r="G11" s="17"/>
+      <c r="A11" s="10"/>
+      <c r="G11" s="13"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>50000</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <f>C10-C6</f>
         <v>136500</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <f t="shared" ref="D12:F12" si="3">D10-D6</f>
         <v>124500</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="5">
         <f t="shared" si="3"/>
         <v>112500</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <f t="shared" si="3"/>
         <v>102000</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <f>F13</f>
         <v>425500</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>50000</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <f>C12-B13</f>
         <v>86500</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <f>C13+D12</f>
         <v>211000</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <f>D13 + E12</f>
         <v>323500</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <f>E13+F12</f>
         <v>425500</v>
       </c>
-      <c r="G13" s="17"/>
+      <c r="G13" s="13"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="14"/>
+      <c r="A14" s="10"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <f>(G10-G6)/G6</f>
         <v>2.0407673860911273</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="8"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="F18" s="18"/>
+      <c r="F18" s="14"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3308,121 +3599,1347 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="15" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A2" s="20">
+      <c r="A2" s="16">
         <v>0</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="16">
         <v>50000</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="16">
         <v>0</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="16">
         <f>B2</f>
         <v>50000</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A3" s="20">
+      <c r="A3" s="16">
         <v>1</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="16">
         <v>45500</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="16">
         <v>182000</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="16">
         <f>D2 +B3</f>
         <v>95500</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="16">
         <f>C3+E2</f>
         <v>182000</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A4" s="20">
+      <c r="A4" s="16">
         <v>2</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="16">
         <v>41500</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="16">
         <v>166000</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="16">
         <f t="shared" ref="D4:D6" si="0">D3 +B4</f>
         <v>137000</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="16">
         <f t="shared" ref="E4:E6" si="1">C4+E3</f>
         <v>348000</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A5" s="21">
+      <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="17">
         <v>37500</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="17">
         <v>150000</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="16">
         <f t="shared" si="0"/>
         <v>174500</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="16">
         <f t="shared" si="1"/>
         <v>498000</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="17" x14ac:dyDescent="0.4">
-      <c r="A6" s="21">
+      <c r="A6" s="17">
         <v>4</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="17">
         <v>34000</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="17">
         <v>136000</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="16">
         <f t="shared" si="0"/>
         <v>208500</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="16">
         <f t="shared" si="1"/>
         <v>634000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="17"/>
+      <c r="A7" s="13"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D85FA164-7CDD-4548-86DB-9537D89ABF5F}">
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="8.7265625" style="2"/>
+    <col min="3" max="3" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="3.7265625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="51" customWidth="1"/>
+    <col min="9" max="9" width="19.26953125" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
+    <col min="11" max="11" width="4.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+    </row>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+    </row>
+    <row r="3" spans="2:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B20" s="30"/>
+      <c r="C20" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K20" s="37"/>
+    </row>
+    <row r="21" spans="2:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="30"/>
+      <c r="C21" s="19">
+        <v>1</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21" s="20">
+        <v>45941</v>
+      </c>
+      <c r="K21" s="37"/>
+    </row>
+    <row r="22" spans="2:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="30"/>
+      <c r="C22" s="19">
+        <v>2</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="K22" s="37"/>
+    </row>
+    <row r="23" spans="2:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="30"/>
+      <c r="C23" s="19">
+        <v>3</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="K23" s="37"/>
+    </row>
+    <row r="24" spans="2:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="30"/>
+      <c r="C24" s="19">
+        <v>4</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="J24" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="K24" s="37"/>
+    </row>
+    <row r="25" spans="2:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="10">
+    <mergeCell ref="B3:K19"/>
+    <mergeCell ref="B1:K2"/>
+    <mergeCell ref="B25:K31"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="K20:K24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BBD680-39B1-4570-8241-E5F4E150A01E}">
+  <dimension ref="B1:M50"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="11" max="11" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B1" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+    </row>
+    <row r="2" spans="2:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B7" s="42"/>
+      <c r="C7" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="42"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B8" s="42"/>
+      <c r="C8" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="42"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B9" s="42"/>
+      <c r="C9" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="42"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B10" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+    </row>
+    <row r="11" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+    </row>
+    <row r="13" spans="2:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="42"/>
+      <c r="C13" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B14" s="42"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B15" s="42"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B16" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+    </row>
+    <row r="17" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B19" s="42"/>
+      <c r="C19" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B20" s="42"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B21" s="42"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B22" s="42"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B23" s="42"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B24" s="42"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B25" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B28" s="40"/>
+      <c r="C28" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="39"/>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B29" s="40"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="39"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B30" s="40"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="39"/>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B31" s="40"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="39"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B32" s="40"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="39"/>
+      <c r="M32" s="39"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B33" s="40"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="39"/>
+      <c r="L33" s="39"/>
+      <c r="M33" s="39"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B34" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="39"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="39"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="39"/>
+      <c r="L35" s="39"/>
+      <c r="M35" s="39"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="39"/>
+      <c r="K36" s="39"/>
+      <c r="L36" s="39"/>
+      <c r="M36" s="39"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B37" s="40"/>
+      <c r="C37" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="39"/>
+      <c r="L37" s="39"/>
+      <c r="M37" s="39"/>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B38" s="40"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="39"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B39" s="40"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B40" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="39"/>
+      <c r="K40" s="39"/>
+      <c r="L40" s="39"/>
+      <c r="M40" s="39"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B41" s="39"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="39"/>
+      <c r="J41" s="39"/>
+      <c r="K41" s="39"/>
+      <c r="L41" s="39"/>
+      <c r="M41" s="39"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B42" s="39"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="39"/>
+      <c r="H42" s="39"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="39"/>
+      <c r="K42" s="39"/>
+      <c r="L42" s="39"/>
+      <c r="M42" s="39"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B43" s="40"/>
+      <c r="C43" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="39"/>
+      <c r="H43" s="39"/>
+      <c r="I43" s="39"/>
+      <c r="J43" s="39"/>
+      <c r="K43" s="39"/>
+      <c r="L43" s="39"/>
+      <c r="M43" s="39"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B44" s="40"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="39"/>
+      <c r="H44" s="39"/>
+      <c r="I44" s="39"/>
+      <c r="J44" s="39"/>
+      <c r="K44" s="39"/>
+      <c r="L44" s="39"/>
+      <c r="M44" s="39"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B45" s="40"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="39"/>
+      <c r="H45" s="39"/>
+      <c r="I45" s="39"/>
+      <c r="J45" s="39"/>
+      <c r="K45" s="39"/>
+      <c r="L45" s="39"/>
+      <c r="M45" s="39"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B46" s="40"/>
+      <c r="C46" s="39"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="39"/>
+      <c r="F46" s="39"/>
+      <c r="G46" s="39"/>
+      <c r="H46" s="39"/>
+      <c r="I46" s="39"/>
+      <c r="J46" s="39"/>
+      <c r="K46" s="39"/>
+      <c r="L46" s="39"/>
+      <c r="M46" s="39"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B47" s="40"/>
+      <c r="C47" s="39"/>
+      <c r="D47" s="39"/>
+      <c r="E47" s="39"/>
+      <c r="F47" s="39"/>
+      <c r="G47" s="39"/>
+      <c r="H47" s="39"/>
+      <c r="I47" s="39"/>
+      <c r="J47" s="39"/>
+      <c r="K47" s="39"/>
+      <c r="L47" s="39"/>
+      <c r="M47" s="39"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B48" s="41"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="41"/>
+      <c r="I48" s="41"/>
+      <c r="J48" s="41"/>
+      <c r="K48" s="41"/>
+      <c r="L48" s="41"/>
+      <c r="M48" s="41"/>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41"/>
+      <c r="J49" s="41"/>
+      <c r="K49" s="41"/>
+      <c r="L49" s="41"/>
+      <c r="M49" s="41"/>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B50" s="41"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="41"/>
+      <c r="J50" s="41"/>
+      <c r="K50" s="41"/>
+      <c r="L50" s="41"/>
+      <c r="M50" s="41"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="26">
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="B2:M6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:L7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:L8"/>
+    <mergeCell ref="C13:M15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B16:M18"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="B10:M12"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:L9"/>
+    <mergeCell ref="B48:M50"/>
+    <mergeCell ref="C19:M24"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="B25:M27"/>
+    <mergeCell ref="C28:M33"/>
+    <mergeCell ref="B28:B33"/>
+    <mergeCell ref="B34:M36"/>
+    <mergeCell ref="C37:M39"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:M42"/>
+    <mergeCell ref="C43:M47"/>
+    <mergeCell ref="B43:B47"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>